--- a/Excel/Excel Workbook/AVERAGEIFS Example.xlsx
+++ b/Excel/Excel Workbook/AVERAGEIFS Example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\My Projects\Data Projects\My Data Science Full Kit\Complete_Data_Science_Full_Course\Excel\Excel Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BC6E44-5680-4257-992D-817C4A6FD85E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C811CFFF-B563-4D62-AA66-1E16D2B5FFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -419,6 +419,7 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="19.1796875" customWidth="1"/>
     <col min="8" max="8" width="17.08984375" customWidth="1"/>
   </cols>
   <sheetData>

--- a/Excel/Excel Workbook/AVERAGEIFS Example.xlsx
+++ b/Excel/Excel Workbook/AVERAGEIFS Example.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\My Projects\Data Projects\My Data Science Full Kit\Complete_Data_Science_Full_Course\Excel\Excel Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C811CFFF-B563-4D62-AA66-1E16D2B5FFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B13BF370-1C7F-4B5D-BF1C-265A52A389EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="15600" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -420,7 +420,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.1796875" customWidth="1"/>
-    <col min="8" max="8" width="17.08984375" customWidth="1"/>
+    <col min="8" max="8" width="29.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
